--- a/data/Copilot_Beispiel.xlsx
+++ b/data/Copilot_Beispiel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gollnickdatasolutions-my.sharepoint.com/personal/bertgollnick_gollnickdatasolutions_onmicrosoft_com/Documents/Projects/Bildungsurlaub/KIfürJobUndAlltag/Inhalte/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{8FA7408D-3C2B-4F53-A247-F32E65FC1004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F7C8656-644F-4DB3-AA2A-9A5782295704}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{8FA7408D-3C2B-4F53-A247-F32E65FC1004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F03B5633-C749-4378-9F07-40BF552FE44E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{9FC30950-8112-467D-B040-64EA03D87939}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9FC30950-8112-467D-B040-64EA03D87939}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Ich habe einhundert € für das Abo bezahlt.</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>Netflix kostet mittlerweile zehn Euronen im Monat.</t>
-  </si>
-  <si>
-    <t>franziska.rueckert@drv-bund.de; Markus Güntther &lt;markus.guenther.inbox@outlook.de&gt;; Matthias Täubrich &lt;matthias@taeubrich.de&gt;; blauth.timo@yahoo.de; sarah.roesener@web.de; Jesko Rehberg &lt;jesko.rehberg@dar-analytics.de&gt;; franziskarueckert@gmx.net</t>
   </si>
 </sst>
 </file>
@@ -122,6 +119,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -441,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABA0037-5822-4E2F-98F7-674D229CE257}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.5703125" bestFit="1" customWidth="1"/>
@@ -466,11 +467,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
